--- a/大文件传输平台特性清单_v2.xlsx
+++ b/大文件传输平台特性清单_v2.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="139">
   <si>
     <t>一级特性</t>
   </si>
@@ -74,7 +74,13 @@
     <t>选择传输类型</t>
   </si>
   <si>
-    <t>绿区/黄区/红区/内网/外网间传输类型选择</t>
+    <t>绿区/黄区/外网跨域传输类型选择</t>
+  </si>
+  <si>
+    <t>红区与绿黄外跨域传输</t>
+  </si>
+  <si>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>创建申请单</t>
@@ -89,22 +95,10 @@
     <t>我的申请单分页查询、筛选、搜索、详情查看</t>
   </si>
   <si>
-    <t>草稿管理</t>
-  </si>
-  <si>
-    <t>草稿列表展示、继续编辑、删除</t>
-  </si>
-  <si>
-    <t>个人中心</t>
-  </si>
-  <si>
-    <t>个人信息查看编辑、密码修改</t>
-  </si>
-  <si>
-    <t>消息中心</t>
-  </si>
-  <si>
-    <t>站内消息接收、已读标记、详情查看</t>
+    <t>待上传管理</t>
+  </si>
+  <si>
+    <t>待上传列表展示、继续编辑、删除</t>
   </si>
   <si>
     <t>文件传输</t>
@@ -152,6 +146,12 @@
     <t>下载人可见文件列表、下载状态管理</t>
   </si>
   <si>
+    <t>文件夹上传</t>
+  </si>
+  <si>
+    <t>可托选整个文件夹上传</t>
+  </si>
+  <si>
     <t>审批流程</t>
   </si>
   <si>
@@ -179,12 +179,6 @@
     <t>审批人驳回申请、填写驳回原因（10-500字）</t>
   </si>
   <si>
-    <t>免审处理</t>
-  </si>
-  <si>
-    <t>三级审批人/管理员跳过所有审批节点</t>
-  </si>
-  <si>
     <t>审批时间线</t>
   </si>
   <si>
@@ -245,13 +239,13 @@
     <t>用户管理</t>
   </si>
   <si>
-    <t>用户CRUD、角色分配、状态启用/禁用</t>
+    <t>用户管理、角色分配、状态启用/禁用</t>
   </si>
   <si>
     <t>角色权限</t>
   </si>
   <si>
-    <t>基于RBAC的菜单/操作权限配置</t>
+    <t>菜单/操作权限配置</t>
   </si>
   <si>
     <t>审批流程配置</t>
@@ -275,7 +269,7 @@
     <t>传输通道管理</t>
   </si>
   <si>
-    <t>传输通道CRUD、服务器配置、通道状态切换</t>
+    <t>传输通道、服务器配置、通道状态切换</t>
   </si>
   <si>
     <t>界面配置</t>
@@ -287,7 +281,10 @@
     <t>通知配置</t>
   </si>
   <si>
-    <t>邮件/短信/站内消息通知选项配置</t>
+    <t>邮件通知内容配置</t>
+  </si>
+  <si>
+    <t>welink,短信通知</t>
   </si>
   <si>
     <t>传输服务</t>
@@ -296,13 +293,13 @@
     <t>统一网关</t>
   </si>
   <si>
-    <t>API网关入口、请求路由、负载均衡</t>
+    <t>请求路由、负载均衡</t>
   </si>
   <si>
     <t>任务调度</t>
   </si>
   <si>
-    <t>传输任务智能调度、优先级管理（特急/紧急/普通）</t>
+    <t>传输任务智能调度、优先级管理</t>
   </si>
   <si>
     <t>路由管理</t>
@@ -395,13 +392,25 @@
     <t>日志自动归档、长期存储管理</t>
   </si>
   <si>
+    <t>审计日志外发</t>
+  </si>
+  <si>
+    <t>支持外发到SGP</t>
+  </si>
+  <si>
+    <t>性能边界指标</t>
+  </si>
+  <si>
     <t>安全检测</t>
   </si>
   <si>
     <t>身份认证</t>
   </si>
   <si>
-    <t>账号密码认证、SSO单点登录支持</t>
+    <t>账号密码认证、</t>
+  </si>
+  <si>
+    <t>SSO单点登录支持</t>
   </si>
   <si>
     <t>权限控制</t>
@@ -419,7 +428,10 @@
     <t>文件安全</t>
   </si>
   <si>
-    <t>文件类型校验、病毒扫描（可选）、文件加密存储</t>
+    <t>文件类型校验、文件加密存储</t>
+  </si>
+  <si>
+    <t>文件支持传到恶意文件检测（高）</t>
   </si>
   <si>
     <t>XSS防护</t>
@@ -444,7 +456,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -456,13 +468,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -612,7 +617,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -633,6 +638,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFCE4D6"/>
         <bgColor rgb="FFFCE4D6"/>
       </patternFill>
@@ -824,7 +835,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -842,6 +853,43 @@
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -948,163 +996,190 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1453,13 +1528,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
-    <col min="4" max="4" width="32" customWidth="1"/>
+    <col min="4" max="4" width="49.3185840707965" customWidth="1"/>
     <col min="5" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1490,1140 +1565,993 @@
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="E2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A9" s="5"/>
+      <c r="B9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A15" s="7"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A16" s="8"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A17" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="B17" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A22" s="8"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A23" s="8"/>
+      <c r="B23" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A25" s="8"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A20" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A24" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="26" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A26" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="A26" s="8"/>
+      <c r="B26" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="C26" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" s="2" t="s">
+      <c r="D26" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="27" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A27" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" s="2" t="s">
+      <c r="E27" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="28" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A28" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C28" s="2" t="s">
+      <c r="A28" s="8"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" s="2" t="s">
+      <c r="E28" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="29" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A29" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="A29" s="8"/>
       <c r="B29" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C29" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="C29" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" s="2" t="s">
+      <c r="D29" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="30" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A30" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C30" s="2" t="s">
+      <c r="A30" s="8"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="E30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>11</v>
+      <c r="E30" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C31" s="2" t="s">
+      <c r="A31" s="8"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="E31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>11</v>
+      <c r="E31" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="32" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A32" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C32" s="2" t="s">
+      <c r="A32" s="8"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>11</v>
+      <c r="E32" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="33" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A33" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C33" s="2" t="s">
+      <c r="A33" s="8"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="E33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>11</v>
+      <c r="E33" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="34" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A34" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C34" s="2" t="s">
+      <c r="A34" s="8"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="E34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>11</v>
+      <c r="E34" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="35" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A35" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C35" s="2" t="s">
+      <c r="A35" s="8"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="E35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" s="2" t="s">
+      <c r="E35" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="36" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A36" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>70</v>
-      </c>
+      <c r="A36" s="8"/>
+      <c r="B36" s="5"/>
       <c r="C36" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="E36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" s="2" t="s">
+      <c r="E36" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="37" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A37" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C37" s="2" t="s">
+      <c r="A37" s="8"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="E37" s="4"/>
+      <c r="F37" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A38" s="8"/>
+      <c r="B38" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="E37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="38" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A38" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B38" s="2" t="s">
+      <c r="C38" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="D38" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="E38" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A39" s="8"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="39" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A39" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C39" s="2" t="s">
+      <c r="D39" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="E39" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A40" s="8"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E39" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="40" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A40" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C40" s="2" t="s">
+      <c r="D40" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="E40" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A41" s="8"/>
+      <c r="B41" s="10"/>
+      <c r="C41" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E40" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="41" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A41" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C41" s="2" t="s">
+      <c r="D41" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="E41" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A42" s="8"/>
+      <c r="B42" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="E41" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="42" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A42" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B42" s="2" t="s">
+      <c r="C42" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="D42" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="E42" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="F42" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A43" s="8"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="F42" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="43" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A43" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C43" s="2" t="s">
+      <c r="D43" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="E43" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A44" s="8"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E43" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="44" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A44" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C44" s="2" t="s">
+      <c r="D44" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="E44" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A45" s="10"/>
+      <c r="B45" s="10"/>
+      <c r="C45" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="E44" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="45" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A45" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C45" s="2" t="s">
+      <c r="D45" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="E45" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A46" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="E45" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="46" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A46" s="2" t="s">
+      <c r="B46" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="C46" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="D46" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="E46" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A47" s="8"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E46" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="47" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A47" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C47" s="2" t="s">
+      <c r="D47" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="E47" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A48" s="8"/>
+      <c r="B48" s="8"/>
+      <c r="C48" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E47" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="48" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A48" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C48" s="2" t="s">
+      <c r="D48" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="E48" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A49" s="8"/>
+      <c r="B49" s="8"/>
+      <c r="C49" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E48" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="49" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A49" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C49" s="2" t="s">
+      <c r="D49" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="E49" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A50" s="8"/>
+      <c r="B50" s="8"/>
+      <c r="C50" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="E49" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="50" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A50" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C50" s="2" t="s">
+      <c r="D50" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="E50" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A51" s="8"/>
+      <c r="B51" s="8"/>
+      <c r="C51" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E50" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="51" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A51" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C51" s="2" t="s">
+      <c r="D51" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="E51" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A52" s="8"/>
+      <c r="B52" s="10"/>
+      <c r="C52" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="E51" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="52" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A52" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C52" s="2" t="s">
+      <c r="D52" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="E52" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A53" s="8"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="E52" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="53" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A53" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B53" s="2" t="s">
+      <c r="D53" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="E53" s="13"/>
+      <c r="F53" s="6"/>
+    </row>
+    <row r="54" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A54" s="8"/>
+      <c r="B54" s="8"/>
+      <c r="C54" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="E54" s="13"/>
+      <c r="F54" s="3"/>
+    </row>
+    <row r="55" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A55" s="8"/>
+      <c r="B55" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="E53" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="54" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
-      <c r="A54" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C54" s="2" t="s">
+      <c r="C55" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="D55" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E54" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="55" ht="25" customHeight="1" spans="1:6">
-      <c r="A55" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C55" s="2" t="s">
+      <c r="E55" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A56" s="8"/>
+      <c r="B56" s="8"/>
+      <c r="C56" s="7"/>
+      <c r="D56" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="E56" s="13"/>
+      <c r="F56" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
+      <c r="A57" s="8"/>
+      <c r="B57" s="8"/>
+      <c r="C57" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="E55" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="56" ht="25" customHeight="1" spans="1:6">
-      <c r="A56" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C56" s="2" t="s">
+      <c r="D57" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="E57" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" ht="25" customHeight="1" spans="1:6">
+      <c r="A58" s="8"/>
+      <c r="B58" s="8"/>
+      <c r="C58" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="E56" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="57" ht="25" customHeight="1" spans="1:6">
-      <c r="A57" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C57" s="2" t="s">
+      <c r="D58" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="E58" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" ht="25" customHeight="1" spans="1:6">
+      <c r="A59" s="8"/>
+      <c r="B59" s="8"/>
+      <c r="C59" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="E57" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="58" ht="25" customHeight="1" spans="1:6">
-      <c r="A58" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C58" s="2" t="s">
+      <c r="D59" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="E59" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" ht="25" customHeight="1" spans="1:6">
+      <c r="A60" s="8"/>
+      <c r="B60" s="8"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="E58" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F58" s="2" t="s">
+      <c r="E60" s="13"/>
+      <c r="F60" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="61" ht="25" customHeight="1" spans="1:6">
+      <c r="A61" s="8"/>
+      <c r="B61" s="8"/>
+      <c r="C61" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E61" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" ht="25" customHeight="1" spans="1:6">
+      <c r="A62" s="10"/>
+      <c r="B62" s="10"/>
+      <c r="C62" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E62" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F62" s="3" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A2:A15"/>
+    <mergeCell ref="A17:A45"/>
+    <mergeCell ref="A46:A62"/>
+    <mergeCell ref="B2:B8"/>
+    <mergeCell ref="B9:B16"/>
+    <mergeCell ref="B17:B22"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="B29:B37"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="B46:B52"/>
+    <mergeCell ref="B55:B62"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="C55:C56"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/大文件传输平台特性清单_v2.xlsx
+++ b/大文件传输平台特性清单_v2.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="140">
   <si>
     <t>一级特性</t>
   </si>
@@ -144,6 +144,9 @@
   </si>
   <si>
     <t>下载人可见文件列表、下载状态管理</t>
+  </si>
+  <si>
+    <t>i</t>
   </si>
   <si>
     <t>文件夹上传</t>
@@ -1778,7 +1781,7 @@
         <v>38</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>11</v>
@@ -1788,10 +1791,10 @@
       <c r="A16" s="8"/>
       <c r="B16" s="5"/>
       <c r="C16" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="3" t="s">
@@ -1803,13 +1806,13 @@
         <v>6</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>10</v>
@@ -1822,10 +1825,10 @@
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>10</v>
@@ -1838,10 +1841,10 @@
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>10</v>
@@ -1854,10 +1857,10 @@
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>10</v>
@@ -1870,10 +1873,10 @@
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>10</v>
@@ -1886,10 +1889,10 @@
       <c r="A22" s="8"/>
       <c r="B22" s="10"/>
       <c r="C22" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>10</v>
@@ -1901,13 +1904,13 @@
     <row r="23" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
       <c r="A23" s="8"/>
       <c r="B23" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>10</v>
@@ -1920,10 +1923,10 @@
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>10</v>
@@ -1936,10 +1939,10 @@
       <c r="A25" s="8"/>
       <c r="B25" s="10"/>
       <c r="C25" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>10</v>
@@ -1951,13 +1954,13 @@
     <row r="26" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
       <c r="A26" s="8"/>
       <c r="B26" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>10</v>
@@ -1970,10 +1973,10 @@
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>10</v>
@@ -1986,10 +1989,10 @@
       <c r="A28" s="8"/>
       <c r="B28" s="10"/>
       <c r="C28" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>10</v>
@@ -2001,13 +2004,13 @@
     <row r="29" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
       <c r="A29" s="8"/>
       <c r="B29" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>10</v>
@@ -2020,10 +2023,10 @@
       <c r="A30" s="8"/>
       <c r="B30" s="5"/>
       <c r="C30" s="11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>10</v>
@@ -2036,10 +2039,10 @@
       <c r="A31" s="8"/>
       <c r="B31" s="5"/>
       <c r="C31" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>10</v>
@@ -2052,10 +2055,10 @@
       <c r="A32" s="8"/>
       <c r="B32" s="5"/>
       <c r="C32" s="11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>10</v>
@@ -2068,10 +2071,10 @@
       <c r="A33" s="8"/>
       <c r="B33" s="5"/>
       <c r="C33" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>10</v>
@@ -2084,10 +2087,10 @@
       <c r="A34" s="8"/>
       <c r="B34" s="5"/>
       <c r="C34" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>10</v>
@@ -2100,10 +2103,10 @@
       <c r="A35" s="8"/>
       <c r="B35" s="5"/>
       <c r="C35" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>10</v>
@@ -2116,10 +2119,10 @@
       <c r="A36" s="8"/>
       <c r="B36" s="5"/>
       <c r="C36" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>10</v>
@@ -2133,7 +2136,7 @@
       <c r="B37" s="5"/>
       <c r="C37" s="7"/>
       <c r="D37" s="12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E37" s="4"/>
       <c r="F37" s="6" t="s">
@@ -2143,13 +2146,13 @@
     <row r="38" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
       <c r="A38" s="8"/>
       <c r="B38" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>10</v>
@@ -2162,10 +2165,10 @@
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>10</v>
@@ -2178,10 +2181,10 @@
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>10</v>
@@ -2194,10 +2197,10 @@
       <c r="A41" s="8"/>
       <c r="B41" s="10"/>
       <c r="C41" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>10</v>
@@ -2209,16 +2212,16 @@
     <row r="42" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
       <c r="A42" s="8"/>
       <c r="B42" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>11</v>
@@ -2228,13 +2231,13 @@
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E43" s="13" t="s">
         <v>99</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="E43" s="13" t="s">
-        <v>98</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>11</v>
@@ -2244,13 +2247,13 @@
       <c r="A44" s="8"/>
       <c r="B44" s="8"/>
       <c r="C44" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>11</v>
@@ -2260,13 +2263,13 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>11</v>
@@ -2274,19 +2277,19 @@
     </row>
     <row r="46" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
       <c r="A46" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>11</v>
@@ -2296,13 +2299,13 @@
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>11</v>
@@ -2312,13 +2315,13 @@
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>11</v>
@@ -2328,13 +2331,13 @@
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>11</v>
@@ -2344,13 +2347,13 @@
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>11</v>
@@ -2360,13 +2363,13 @@
       <c r="A51" s="8"/>
       <c r="B51" s="8"/>
       <c r="C51" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>11</v>
@@ -2376,13 +2379,13 @@
       <c r="A52" s="8"/>
       <c r="B52" s="10"/>
       <c r="C52" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>11</v>
@@ -2392,10 +2395,10 @@
       <c r="A53" s="8"/>
       <c r="B53" s="8"/>
       <c r="C53" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E53" s="13"/>
       <c r="F53" s="6"/>
@@ -2404,10 +2407,10 @@
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
       <c r="C54" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E54" s="13"/>
       <c r="F54" s="3"/>
@@ -2415,16 +2418,16 @@
     <row r="55" ht="25" customHeight="1" outlineLevel="1" spans="1:6">
       <c r="A55" s="8"/>
       <c r="B55" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>11</v>
@@ -2435,7 +2438,7 @@
       <c r="B56" s="8"/>
       <c r="C56" s="7"/>
       <c r="D56" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E56" s="13"/>
       <c r="F56" s="6" t="s">
@@ -2446,13 +2449,13 @@
       <c r="A57" s="8"/>
       <c r="B57" s="8"/>
       <c r="C57" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>11</v>
@@ -2462,13 +2465,13 @@
       <c r="A58" s="8"/>
       <c r="B58" s="8"/>
       <c r="C58" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>11</v>
@@ -2478,13 +2481,13 @@
       <c r="A59" s="8"/>
       <c r="B59" s="8"/>
       <c r="C59" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>11</v>
@@ -2495,7 +2498,7 @@
       <c r="B60" s="8"/>
       <c r="C60" s="3"/>
       <c r="D60" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E60" s="13"/>
       <c r="F60" s="6" t="s">
@@ -2506,13 +2509,13 @@
       <c r="A61" s="8"/>
       <c r="B61" s="8"/>
       <c r="C61" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>11</v>
@@ -2522,13 +2525,13 @@
       <c r="A62" s="10"/>
       <c r="B62" s="10"/>
       <c r="C62" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>11</v>
